--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1,37 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="بري فلتر تنظيف" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -79,44 +136,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +200,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +234,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +245,224 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="بري فلتر تنظيف" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="سحب1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,4 +466,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="بري فلتر تنظيف" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="سحب1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="سحب2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,4 +508,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -11,6 +11,7 @@
     <sheet name="بري فلتر تنظيف" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="سحب1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="سحب2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,4 +550,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -12,6 +12,7 @@
     <sheet name="سحب1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="سحب2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -591,4 +592,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -13,6 +13,7 @@
     <sheet name="سحب2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -633,4 +634,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -14,6 +14,7 @@
     <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -675,4 +676,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>تاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -14,7 +14,6 @@
     <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +505,33 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>تم تركيب</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تصحيح </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>صف</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -676,45 +702,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -14,6 +14,7 @@
     <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="محطه التنظيف " sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -702,4 +703,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="محطه التنظيف " sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="محطه غزل2 " sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,4 +740,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,6 +772,80 @@
           <t>تم بواسطه</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Servised by</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Tones</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>انسداد شبكه</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>تم الفك والتنظيف</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>انس,علي,عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -8,14 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="بري فلتر تنظيف" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="سحب1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="سحب2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="سحب3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="محطه التنظيف " sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="محطه غزل2 " sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="محطه التنظيف" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,418 +427,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الحدث</t>
+          <t>التاريخ</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>التصحيح</t>
+          <t>المعدة</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>الحدث/العطل</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>تم بواسطه</t>
+          <t>الإجراء التصحيحي</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>تم بواسطة</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>تم تركيب</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تصحيح </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>صف</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>رقم الماكينه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Equipment</t>
+          <t>الطن</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>الصور</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Correction</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Servised by</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Tones</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Images</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>انسداد شبكه</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>تم الفك والتنظيف</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>انس,علي,عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>ملاحظات</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="محطه التنظيف" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="محطه كرد1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,4 +476,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="محطه التنظيف" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="محطه كرد1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ب" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,4 +533,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -11,6 +11,7 @@
     <sheet name="محطه التنظيف" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="محطه كرد1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ب" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="هب" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,4 +590,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -12,6 +12,7 @@
     <sheet name="محطه كرد1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ب" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="هب" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="كرد1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,4 +647,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,9 +10,19 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="محطه التنظيف" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="محطه كرد1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ب" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="هب" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="كرد1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="محطه كرد2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="المكبس" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="محطه غزل 2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="الضواغط" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="محطه ترطيب الكرد" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="محطه ترطيب التمشيط والبرم" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="محطه ترطيب غزل1" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="محطه ترطيب غزل2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="محطه ترطيب التدوير" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="محطه غزل 1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="محطه التدوير" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="محطه البرم" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="محطه التمشيط" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,6 +435,382 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>انسداد شبك التدوير</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم فك الدنبر الاول والتاني وتنظيف السلك وتركيب</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيز,علي</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -543,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +974,40 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>.55kwموتور</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ناقص زيت</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تغير زيتpg1000
+تغير بليه 6204
+تغير بليه 6202
+تغير بليه 6201
+تغير اولسيه جروبوكس 80*40*10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>شريف ,علي</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -599,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +1064,36 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>جهاز التراب</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تدمير بليه رولر  ماسوره تراب</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تم تغير بليه مقاس UC210</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>م.شحته,م.محمد عبدالله,شريف,انس</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -655,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +1150,186 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>انسداد الشبكه</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تم الفك وتنظيف الشبكه</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>عبدالعظيم,انس</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>الفواصل</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1237,38 +1237,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1293,38 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>الفواصل</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم تغير فواصل البلوك الاول</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>علي،يوسف،احمد عبدالعزيز ،محمود</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,36 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>جهاز التراب</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>هلك فلتر صغير</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم تغير الفلتر بفلتر احتياطي</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>شريف،محمد يحي</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1267,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,38 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1267,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,36 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه الحوض </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تفريغ وغسل الحوض</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,38 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>سيلو5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>سيلو5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,37 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>سيلو5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>صيانه زيت</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تغير زيت جير بوكس درفيل تغذيه السفلي 
+ب2.250كجم زيتpg680</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،احمد عبدالعزيز ،يوسف</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23,6 +23,7 @@
     <sheet name="محطه التدوير" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="محطه البرم" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="محطه التمشيط" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="سحب 1" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,6 +812,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -24,6 +24,7 @@
     <sheet name="محطه البرم" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="محطه التمشيط" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="سحب 1" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="سحب2" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,6 +869,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> رقم الماكينة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,6 +863,52 @@
           <t>ملاحظات</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>رقم الماكينة</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تركيب</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تم تشغيل</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>صافي</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>سحب اول</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -886,7 +932,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> رقم الماكينة</t>
+          <t>رقم الماكينة</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,6 +965,52 @@
           <t>قسم</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تركيب</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تم تشغيل</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>صافي</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>سحب اول</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23,8 +23,10 @@
     <sheet name="محطه التدوير" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="محطه البرم" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="محطه التمشيط" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="سحب 1" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="سحب2" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="محطه تحليه المياه" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="الغزل" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="تمشيط" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ملفات" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,6 +625,50 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>انسداد شبك التدوير</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم التنظيف والتركيب</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">علي،احمد الصادق </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -635,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +713,160 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
         </is>
       </c>
     </row>
@@ -681,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,6 +915,190 @@
           <t>الصور</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>تغيير جربوكس</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم تغييرجربوكس</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>انس واحمدالصادق</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -727,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +1143,160 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
         </is>
       </c>
     </row>
@@ -773,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +1343,208 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>بري فلتر2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>بري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>بري فلتر2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
         </is>
       </c>
     </row>
@@ -819,7 +1559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,52 +1603,20 @@
           <t>ملاحظات</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>رقم الماكينة</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>تركيب</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>تم تشغيل</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>صافي</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">براميل الملح </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>سحب اول</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -921,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,7 +1640,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>رقم الماكينة</t>
+          <t>المعدة</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -962,55 +1670,220 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>قسم</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>تركيب</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>تم تشغيل</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>صافي</t>
-        </is>
-      </c>
+          <t>غزل ١</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>سحب اول</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>غزل ١</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>تغيير مقص 1530</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم التغيير
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محمد شاهين </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>عوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تغير الاندكس من 9.5ل9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ابراهيم السيد</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>العوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>العوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1023,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,6 +1940,231 @@
           <t>ملاحظات</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">روتاري فلتر التنظيف </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي شحم EB2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>شريف وعبد الحميد</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>تشحيم</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>قطع سير الرئيسي</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغيير السير الرئيسي
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ماكينه 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ماكينه 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>قطع سير رائيسي</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تغيير السير وتركيب سير قديم</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1079,7 +2177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +2221,94 @@
           <t>ملاحظات</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي الفلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>شريف و عبد الحميد</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي البري فلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف وعبد الحميد</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1135,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +2399,94 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">روتاري فلتر </t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي الفلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>شريف و عبد الحميد</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي البري فلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف وعبد الحميد</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1225,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,45 +2575,47 @@
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>جهاز التراب</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>هلك فلتر صغير</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تم تغير الفلتر بفلتر احتياطي</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>شريف،محمد يحي</t>
-        </is>
-      </c>
+          <t>سيلو5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>سيلو5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>تغير زيت</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم تغير زيت جير بوكس درافيل  تغزيه  
+بزيتPG680  
+كميه 2,25كجم</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>شريف,يوسف,احمد عبدالعزيز</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -1347,51 +2623,236 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>سيلو5</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>جهاز التراب</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>هلك فلتر صغير</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم الاستبدال بفلتر احتياطي</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>محمد يحي</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>سيلو5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>صيانه زيت</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>تم تغير زيت جير بوكس درفيل تغذيه السفلي 
-ب2.250كجم زيتpg680</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف،احمد عبدالعزيز ،يوسف</t>
-        </is>
-      </c>
+          <t>مكبس السايلوهات</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>جهاز التراب</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مكبس التمشيط </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مكبس التمشيط </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>مكبس التمشيط</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>فلتر زيت</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تغير فولتير الزيت </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>شريف و عبدالحميد</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>جهاز التراب</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تلف فلتر هواء كبير </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم استبدال </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محمد عبدالله </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>سيلو5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تغير زيت جير بوكس فايبر  سيباراتور </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>شريف،محروس،محمد سامح</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>زيتclp pg 680
+الكميه=1كجم</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>سيلوا4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>سيلوا4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تغير زيت جير بوكس فايبر  سيباراتور </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>شريف،محروس،محمد سامح</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>زيتclp pg 680
+الكميه=1كجم</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1404,7 +2865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,6 +2939,150 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1536,7 +3141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,7 +3190,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الفواصل</t>
+          <t>الحوض</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -1596,45 +3201,45 @@
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>الفواصل</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تم تغير فواصل البلوك الاول</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>علي،يوسف،احمد عبدالعزيز ،محمود</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحوض</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم تفريغ وغسل وملئ حوض</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -1647,45 +3252,131 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>الفواصل</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تغير فواصل بلوك الاول</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانه الحوض </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>تم تفريغ وغسل الحوض</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنظيف شبك الدنابر </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>محروس،محمود،انس</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم تفريغ الحوض وتنظيفه وملئه</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>تم تنظيف الشبك وغسله وتركيبه</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>علاء،الصادق</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -27,6 +27,8 @@
     <sheet name="الغزل" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="تمشيط" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="ملفات" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="قطع_الغيار" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="صيانة_وقائية" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +37,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -65,8 +70,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2171,6 +2177,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>اسم القطعة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>اسم الماكينة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>نوع_الصيانة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>اسم_البند</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الفترة_بالأيام</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>آخر_تنفيذ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>التاريخ_التالي</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>قطع_غيار_مستخدمة_افتراضية</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>شهرية</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/maintenance_task/maintenance_task_b04fdd3c_20260415_174315.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -38,8 +38,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -3290,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3332,6 +3332,36 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -3348,6 +3378,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -3362,6 +3398,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3392,6 +3434,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3422,6 +3470,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -3436,6 +3490,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3466,6 +3526,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3496,6 +3562,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3526,6 +3598,64 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنظيف الشبك </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>هيكلي</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/event/event_a0bc0643_20260415_183500.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -3290,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3654,6 +3654,58 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/event/event_a0bc0643_20260415_183500.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>تم</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>هيكلي</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>غير ملتزم</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/event/event_0d00a95c_20260415_185214.jpg</t>
         </is>
       </c>
     </row>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,6 +2220,41 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>موتور</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>.55</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>.55kwموتور</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/spare_part/spare_part_17e07b65_20260415_195132.jpg</t>
         </is>
       </c>
     </row>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2229,18 +2229,14 @@
           <t>موتور</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>.55</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.55</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -37,9 +37,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -70,9 +72,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2265,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2345,6 +2348,33 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/maintenance_task/maintenance_task_b04fdd3c_20260415_174315.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>غسيل</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2368,7 +2368,9 @@
       <c r="D3" t="n">
         <v>7</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="1" t="n">
+        <v>46127</v>
+      </c>
       <c r="F3" s="2" t="n">
         <v>46134</v>
       </c>
@@ -3351,7 +3353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3769,6 +3771,54 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/event/event_0d00a95c_20260415_185214.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: غسيل</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'غسيل'</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>نظام الصيانة الوقائية</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1739,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1781,6 +1781,36 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -1797,6 +1827,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1827,6 +1863,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1841,6 +1883,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1867,6 +1915,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1893,6 +1947,60 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم البنوز'</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>نظام الصيانة الوقائية</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2337,9 +2445,11 @@
       <c r="D2" t="n">
         <v>30</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46157</v>
+      <c r="E2" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46159</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2371,7 +2481,7 @@
       <c r="E3" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="G3" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1739,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,6 +2001,54 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم البنوز' بواسطة حماده</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2446,12 +2494,16 @@
         <v>30</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46129</v>
+        <v>46119</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>46149</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-07 | تم بواسطة: حماده</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1739,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,6 +2049,54 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم البنوز' بواسطة حماده</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2501,7 +2549,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-07 | تم بواسطة: حماده</t>
+          <t>2026-04-07 | تم بواسطة: حماده
+2026-04-07 | تم بواسطة: حماده</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2472,7 +2472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2544,7 +2544,7 @@
       <c r="E2" s="1" t="n">
         <v>46119</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -2588,6 +2588,33 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4000 ساعة</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>تنظيف السلك</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>166.6666666666667</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -37,11 +37,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -72,10 +70,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2390,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2460,6 +2457,33 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/spare_part/spare_part_17e07b65_20260415_195132.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>شحم ep2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2609,7 +2633,7 @@
         <v>166.6666666666667</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>46293</v>
       </c>
       <c r="G4" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -37,9 +37,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -70,9 +72,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1736,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2097,58 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم البنوز' بواسطة علي</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>شحم ep2 (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2466,12 +2521,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2566,15 +2619,16 @@
         <v>30</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>46149</v>
+        <v>46128</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46158</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-04-07 | تم بواسطة: حماده
-2026-04-07 | تم بواسطة: حماده</t>
+2026-04-07 | تم بواسطة: حماده
+2026-04-16 | تم بواسطة: علي | استخدمت شحم ep2 كمية 1 - تم خصم 1 من 'شحم ep2'، الرصيد الجديد: 5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2628,7 +2628,8 @@
         <is>
           <t>2026-04-07 | تم بواسطة: حماده
 2026-04-07 | تم بواسطة: حماده
-2026-04-16 | تم بواسطة: علي | استخدمت شحم ep2 كمية 1 - تم خصم 1 من 'شحم ep2'، الرصيد الجديد: 5</t>
+2026-04-16 | تم بواسطة: علي | استخدمت شحم ep2 كمية 1 - تم خصم 1 من 'شحم ep2'، الرصيد الجديد: 5
+2026-04-16 | تم بواسطة: علي</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,7 +2621,7 @@
       <c r="E2" s="1" t="n">
         <v>46128</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>46158</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -2694,6 +2694,33 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>.55kwموتور</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>زيت</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1739,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2149,54 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم البنوز</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم البنوز' بواسطة ص</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ص</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2619,17 +2667,18 @@
         <v>30</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>46158</v>
+        <v>46129</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46159</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-04-07 | تم بواسطة: حماده
 2026-04-07 | تم بواسطة: حماده
 2026-04-16 | تم بواسطة: علي | استخدمت شحم ep2 كمية 1 - تم خصم 1 من 'شحم ep2'، الرصيد الجديد: 5
-2026-04-16 | تم بواسطة: علي</t>
+2026-04-16 | تم بواسطة: علي
+2026-04-17 | تم بواسطة: ص</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -2715,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>46130</v>
       </c>
       <c r="G5" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -37,12 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -72,10 +67,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2597,7 +2590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2646,130 +2639,6 @@
           <t>رابط_الصورة</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10تمشيط</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>شهرية</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>تشحيم البنوز</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46129</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-04-07 | تم بواسطة: حماده
-2026-04-07 | تم بواسطة: حماده
-2026-04-16 | تم بواسطة: علي | استخدمت شحم ep2 كمية 1 - تم خصم 1 من 'شحم ep2'، الرصيد الجديد: 5
-2026-04-16 | تم بواسطة: علي
-2026-04-17 | تم بواسطة: ص</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mahmedabdallh123/Elqds/main/event_images/maintenance_task/maintenance_task_b04fdd3c_20260415_174315.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>أسبوعية</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>غسيل</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4000 ساعة</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>تنظيف السلك</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>166.6666666666667</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>.55kwموتور</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>24 ساعة</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>زيت</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>46130</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2578,6 +2578,33 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2202,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2244,6 +2244,36 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -2260,6 +2290,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2290,6 +2326,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -2304,6 +2346,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2334,6 +2382,42 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>سير  (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2585,13 +2669,11 @@
           <t xml:space="preserve">سير </t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5555</t>
-        </is>
+      <c r="B4" t="n">
+        <v>5555</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,6 +29,7 @@
     <sheet name="ملفات" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="قطع_الغيار" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="صيانة_وقائية" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="الكرد" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2754,6 +2755,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2761,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2820,6 +2820,23 @@
           <t>رابط الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -38,7 +38,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -68,8 +71,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2700,7 +2704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2749,6 +2753,37 @@
           <t>رابط_الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تشحيم السلندر</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>45503</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>شحمep2=15جم</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -38,9 +38,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -71,9 +73,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2704,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,6 +2787,37 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>تشحيم الدوفر</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>45503</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>شحمep2=8جم</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2707,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2808,7 +2808,7 @@
         <v>180</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>45503</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -2818,6 +2818,33 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15000 ساعة</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>تغير زيت جير بوكس الفلاتس</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>625</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2707,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2839,12 +2839,39 @@
         <v>625</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>45948</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>40000 ساعة</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>تغير زيت جير بوكس DFK</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1666.666666666667</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>46989</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2707,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2866,12 +2866,39 @@
         <v>1666.666666666667</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>46989</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>40000 ساعة</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>تغير زيت جير بوكس فيد رولل</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1666.666666666667</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>46989</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2776,13 +2776,16 @@
       <c r="D2" t="n">
         <v>180</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>45503</v>
+      <c r="E2" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46310</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>شحمep2=15جم</t>
+          <t>شحمep2=15جم
+2026-04-18 | تم بواسطة: تيم الكرد</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -2893,7 +2896,7 @@
         <v>1666.666666666667</v>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>46989</v>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -2911,7 +2914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2987,6 +2990,51 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم السلندر</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم السلندر' بواسطة تيم الكرد</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>تيم الكرد</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2779,7 +2779,7 @@
       <c r="E2" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>46310</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -2810,13 +2810,16 @@
       <c r="D3" t="n">
         <v>180</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>45503</v>
+      <c r="E3" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>46310</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>شحمep2=8جم</t>
+          <t>شحمep2=8جم
+2026-04-18 | تم بواسطة: تيم الكرد</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -2914,7 +2917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3035,6 +3038,51 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم الدوفر</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم الدوفر' بواسطة تيم الكرد</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>تيم الكرد</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2813,7 +2813,7 @@
       <c r="E3" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>46310</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -2844,11 +2844,17 @@
       <c r="D4" t="n">
         <v>625</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>45948</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>46755</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-18 | تم بواسطة: تيم الكرد</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2917,7 +2923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3083,6 +3089,51 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تغير زيت جير بوكس الفلاتس</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير زيت جير بوكس الفلاتس' بواسطة تيم الكرد</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>تيم الكرد</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -2707,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2847,7 +2847,7 @@
       <c r="E4" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>46755</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -2911,6 +2911,33 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1تغير زيت جير بوكس فيد رولل</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -31,6 +31,7 @@
     <sheet name="صيانة_وقائية" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="التفتيح" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="البرم" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="سحب1" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,11 +40,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -74,10 +73,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3223,7 +3221,7 @@
       <c r="E15" s="1" t="n">
         <v>46125</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>47037</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -4262,6 +4260,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -32,6 +32,7 @@
     <sheet name="التفتيح" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="البرم" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="سحب1" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="سحب2" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4331,6 +4332,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -33,6 +33,7 @@
     <sheet name="البرم" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="سحب1" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="سحب2" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="الكرد" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4403,6 +4404,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -31,9 +31,10 @@
     <sheet name="صيانة_وقائية" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="التفتيح" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="البرم" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="سحب1" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="سحب2" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="الكرد" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="سحب اول" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="سحب ثاني" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="المحطات" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="الكرد" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1741,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2277,6 +2278,52 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>تمشيط4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حدوث حريق </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>تم السيطره ع حريق وتسغيل</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>تيم تمشيط</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_882dc9a7_20260422_210719.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2336,11 +2383,7 @@
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">روتاري فلتر التنظيف </t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -2380,11 +2423,7 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>بري فلتر</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -2717,7 +2756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3494,6 +3533,809 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>تشحيم البلي</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>180</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شحم Ep2 </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>روتاري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>تشحيم البلي</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>180</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شحم Ep2 </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>بري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>180</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>180</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>180</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>180</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>180</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>180</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>180</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>180</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>180</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>180</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>180</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>180</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>180</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>180</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>180</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>180</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>180</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>180</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>180</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>180</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4320 ساعة</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>180</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>شحمEp2
+2026-04-10 | تم بواسطة: شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>سحب1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>تشحيم</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3506,7 +4348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3569,11 +4411,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BOP</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -3586,11 +4424,7 @@
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CLX-1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -3603,11 +4437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CLX-2</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -3620,11 +4450,7 @@
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MIX-2</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -3637,11 +4463,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MIX-1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -3654,11 +4476,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CLU-1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -3671,11 +4489,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CLU-2</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -3688,11 +4502,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TS-T5-2</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -3705,11 +4515,7 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TS-T5-1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -3722,11 +4528,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SP-MF</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -3739,11 +4541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BO-R</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -3754,8 +4552,10 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>0</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3788,8 +4588,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>5</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3803,8 +4605,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>0</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3837,8 +4641,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>5</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -3848,8 +4654,10 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>0</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3882,8 +4690,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>5</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -3893,8 +4703,10 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>0</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3927,8 +4739,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>5</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3938,8 +4752,10 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>0</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3972,8 +4788,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>5</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -3983,8 +4801,10 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>0</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4017,8 +4837,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>5</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4028,8 +4850,10 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>0</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4062,8 +4886,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>5</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -4073,8 +4899,10 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>0</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4107,8 +4935,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>5</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4116,6 +4946,96 @@
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>حدوث حريق ف جوان مضرب تفتيح</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم الفك وتنظيف وتركيب جوان جديد </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ايهاب</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_6ec87bc7_20260422_205831.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TS-T5-1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>(F1)عطل ف كاميرا</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>تم معايره الكاميرا</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">م.محمد عبدالله </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>كهربائي</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_25421959_20260423_181555.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4128,7 +5048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4256,6 +5176,62 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>برم7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>برم7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>تم تركيب ڤالف ع جهاز تنظيف  زراع رقم2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>اسامه</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4268,7 +5244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4325,6 +5301,151 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سحب1 </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>سحب2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>سحب3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>سحب5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>سحب6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تلف بيليه شداد الكويلر وتغير سير شداد</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>تم تغيير 2 بلية شداد سير الكولير  وتغيير سير  2083PJ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_85ea4b35_20260420_172837.jpg</t>
         </is>
       </c>
     </row>
@@ -4339,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4396,6 +5517,117 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>سحب1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>سحب2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>سحب3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تغيير 2كورسي  السلندر امامي </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_de898a02_20260420_172340.jpg</t>
         </is>
       </c>
     </row>
@@ -4410,7 +5642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4467,6 +5699,1534 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بري فلتر التنظيف </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بري فلتر كرد1 </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>بري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>طرمبه حوض البرم</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>طرمبه حوض البرم</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>انسداد الطرمبه</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>تم الفك والتنظيف والتركيب</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_84e826d3_20260420_193315.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>دنابر محطه غزل1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>كرد23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>كرد23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تلف سير700</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>تم تغيير سير عصارت700 بسبب تأكل السير 
+وتم حل العصارات تم التأكد من جودتها</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>عمر</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_1cd08ed2_20260422_210349.jpg</t>
         </is>
       </c>
     </row>
@@ -4558,11 +7318,7 @@
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>روتاري فلتر</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -4614,11 +7370,7 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>بري فلتر</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -4697,8 +7449,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0.5</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -4706,8 +7460,10 @@
           <t>ميكانيكي</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -4812,11 +7568,7 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">روتاري فلتر </t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -4856,11 +7608,7 @@
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>بري فلتر</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -5022,11 +7770,7 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>سيلو5</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -5160,11 +7904,7 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مكبس التمشيط </t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -5180,11 +7920,7 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مكبس التمشيط </t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -5313,11 +8049,7 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>سيلوا4</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -5401,8 +8133,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>0</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -5410,8 +8144,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>5</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5449,8 +8185,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>0</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -5458,8 +8196,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>5</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5521,8 +8261,10 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -5530,8 +8272,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>5</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5569,8 +8313,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -5578,8 +8324,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>5</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5617,8 +8365,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>0</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -5626,8 +8376,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>5</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5658,11 +8410,7 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>سيلو2</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -5725,8 +8473,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>0</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -5734,8 +8484,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>5</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -5777,8 +8529,10 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>0</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -5786,8 +8540,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>5</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -5829,8 +8585,10 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>0</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -5838,8 +8596,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>5</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7,33 +7,32 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="محطه التنظيف" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="محطه كرد1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="محطه كرد2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="المكبس" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="محطه غزل 2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="الضواغط" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="محطه ترطيب الكرد" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="محطه ترطيب التمشيط والبرم" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="محطه ترطيب غزل1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="محطه ترطيب غزل2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="محطه ترطيب التدوير" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="محطه غزل 1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="محطه التدوير" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="محطه البرم" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="محطه التمشيط" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="محطه تحليه المياه" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="الغزل" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="تمشيط" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ملفات" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="قطع_الغيار" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="صيانة_وقائية" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="التفتيح" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="البرم" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="سحب اول" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="سحب ثاني" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="المحطات" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="الكرد" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="محطه كرد1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="محطه كرد2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="المكبس" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="محطه غزل 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="الضواغط" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="محطه ترطيب الكرد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="محطه ترطيب التمشيط والبرم" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="محطه ترطيب غزل1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="محطه ترطيب غزل2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="محطه ترطيب التدوير" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="محطه غزل 1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="محطه التدوير" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="محطه البرم" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="محطه التمشيط" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="محطه تحليه المياه" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="الغزل" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="تمشيط" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ملفات" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="قطع_الغيار" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="صيانة_وقائية" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="التفتيح" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="البرم" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="سحب اول" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="سحب ثاني" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="المحطات" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="الكرد" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,2208 +442,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>روتاري فلتر التنظيف</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>شحم</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تم تشحيم الكراسي شحم EB2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>شريف وعبد الحميد</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>بري فلتر</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>تشحيم</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>تم تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>انسداد شبك التدوير</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تم فك الدنبر الاول والتاني وتنظيف السلك وتركيب</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>احمد عبالعزيز,علي</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>انسداد شبك التدوير</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>تم التنظيف والتركيب</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">علي،احمد الصادق </t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>تغيير جربوكس</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>تم تغييرجربوكس</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>انس واحمدالصادق</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>روتاري فلتر3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>بري فلتر2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>بري فلتر1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>بري فلتر1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>بري فلتر2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>روتاري فلتر1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>روتاري فلتر2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تشحيم </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>شحم=Ep2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">براميل الملح </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>غزل ١</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>غزل ١</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>تغيير مقص 1530</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم التغيير
-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">محمد شاهين </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10تمشيط</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10تمشيط</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>عوادم عاليه</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تغير الاندكس من 9.5ل9</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ابراهيم السيد</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ماكينه 9</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ماكينه 9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>العوادم عاليه</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ماكينه 9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>العوادم عاليه</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>تمشيط1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>تمشيط4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>تمشيط12</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>تمشيط4</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>تم تغير حامل مشط علوي</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>تمشيط12</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>تم تغير حامل تقليع الملف</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>تمشيط7</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>تمشيط12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>تم عيار الفرش</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ملتزم جزئياً</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>تمشيط4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>تلف سير1000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>تم الاستبدال بواحد قديم مؤقتا</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ملتزم جزئياً</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>تمشيط13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>تمشيط13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>تم  تغير2 جلبه تغزيه</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ملتزم جزئياً</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>تمشيط4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حدوث حريق </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>تم السيطره ع حريق وتسغيل</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>تيم تمشيط</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_882dc9a7_20260422_210719.jpg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>قطع سير الرئيسي</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تغيير السير الرئيسي
-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ماكينه 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ماكينه 1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>قطع سير رائيسي</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>تغيير السير وتركيب سير قديم</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ماكينه 1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>كسر الشداد</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>تم الحام والتركيب</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2885,7 +682,2027 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>انسداد شبك التدوير</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تم فك الدنبر الاول والتاني وتنظيف السلك وتركيب</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيز,علي</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>انسداد شبك التدوير</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم التنظيف والتركيب</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">علي،احمد الصادق </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>تغيير جربوكس</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم تغييرجربوكس</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>انس واحمدالصادق</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>روتاري فلتر3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>بري فلتر2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>بري فلتر1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>بري فلتر2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>روتاري فلتر2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تشحيم </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تشحيم كراسي تحميل </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">براميل الملح </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>غزل ١</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>غزل ١</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>تغيير مقص 1530</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم التغيير
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محمد شاهين </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10تمشيط</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>عوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>تغير الاندكس من 9.5ل9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ابراهيم السيد</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>العوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ماكينه 9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>العوادم عاليه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تغيير الاندكس من 9.5ال 9لتقليل العوادم</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>تمشيط4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>تمشيط12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>تمشيط4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>تم تغير حامل مشط علوي</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>تمشيط12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>تم تغير حامل تقليع الملف</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>تمشيط7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>تمشيط12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>تم عيار الفرش</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>تمشيط4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>تلف سير1000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>تم الاستبدال بواحد قديم مؤقتا</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>تمشيط13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>تمشيط13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>تم  تغير2 جلبه تغزيه</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>تمشيط4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حدوث حريق </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>تم السيطره ع حريق وتسغيل</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>تيم تمشيط</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_882dc9a7_20260422_210719.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>قطع سير الرئيسي</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغيير السير الرئيسي
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ماكينه 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ماكينه 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>قطع سير رائيسي</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تغيير السير وتركيب سير قديم</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ماكينه 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>كسر الشداد</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم الحام والتركيب</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2936,7 +2753,177 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>.55kwموتور</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ناقص زيت</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تغير زيتpg1000
+تغير بليه 6204
+تغير بليه 6202
+تغير بليه 6201
+تغير اولسيه جروبوكس 80*40*10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>شريف ,علي</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>روتاري فلتر</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي الفلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>شريف و عبد الحميد</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>شحم</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تم تشحيم الكراسي البري فلتر شحم EB2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>شريف وعبد الحميد</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4528,7 +4515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5228,7 +5215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5418,6 +5405,222 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سحب1 </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>سحب2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>سحب3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>سحب5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>سحب6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تلف بيليه شداد الكويلر وتغير سير شداد</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>تم تغيير 2 بلية شداد سير الكولير  وتغيير سير  2083PJ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_85ea4b35_20260420_172837.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5430,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5495,7 +5698,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سحب1 </t>
+          <t>سحب1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5560,78 +5763,44 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>سحب5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>سحب4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تغيير 2كورسي  السلندر امامي </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>محمود</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>سحب6</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>سحب4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>تلف بيليه شداد الكويلر وتغير سير شداد</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>تم تغيير 2 بلية شداد سير الكولير  وتغيير سير  2083PJ</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_85ea4b35_20260420_172837.jpg</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_de898a02_20260420_172340.jpg</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5711,7 +5880,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>سحب1</t>
+          <t xml:space="preserve">بري فلتر التنظيف </t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5728,7 +5897,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>سحب2</t>
+          <t xml:space="preserve">بري فلتر كرد1 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5745,7 +5914,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>سحب3</t>
+          <t>بري فلتر كرد2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5762,7 +5931,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>سحب4</t>
+          <t>بري فلتر تمشيط1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5776,46 +5945,1331 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>سحب4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تغيير 2كورسي  السلندر امامي </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>محمود</t>
-        </is>
-      </c>
+          <t>بري فلتر تمشيط2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>روتاري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>بري فلتر التنظيف</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>بري فلتر تمشيط2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>شريف ،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>بري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>شريف،عبدالعظيم</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>روتاري فلتر كرد1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل2.1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>روتاري فلتر غزل1.1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تمشيط 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>روتاري فلتر تدوير1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>روتاري فلتر برم1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شريف ،عبدالعظيم </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>طرمبه حوض البرم</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>طرمبه حوض البرم</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>انسداد الطرمبه</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>تم الفك والتنظيف والتركيب</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>ميكانيكي</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_de898a02_20260420_172340.jpg</t>
-        </is>
-      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_84e826d3_20260420_193315.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>دنابر محطه غزل1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5828,7 +7282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5893,7 +7347,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">بري فلتر التنظيف </t>
+          <t>كرد23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5907,1473 +7361,6 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بري فلتر كرد1 </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>بري فلتر كرد2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>بري فلتر تمشيط1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>بري فلتر تمشيط2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>روتاري فلتر التنظيف</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>روتاري فلتر كرد1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>روتاري فلتر كرد2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تمشيط 1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تمشيط 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>بري فلتر التنظيف</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>بري فلتر تمشيط1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>بري فلتر تمشيط2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>بري فلتر كرد1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانة وقائية: تشحيم كراسي التحميل </t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل ' بواسطة شريف ،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>شريف ،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>بري فلتر كرد2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>شريف،عبدالعظيم</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>روتاري فلتر كرد2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>روتاري فلتر كرد1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>0</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.3</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>0</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.2</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>0</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل2.1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>0</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.3</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>0</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.2</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>روتاري فلتر غزل1.1</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>0</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تمشيط 2</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>0</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تمشيط 1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>0</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>روتاري فلتر تدوير1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>5</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>0</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم3</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم2</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>0</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>روتاري فلتر برم1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>صيانة وقائية: تشحيم كراسي التحميل</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'تشحيم كراسي التحميل' بواسطة شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شريف ،عبدالعظيم </t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>صيانة وقائية</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ملتزم بالكامل</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>طرمبه حوض البرم</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>طرمبه حوض البرم</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>انسداد الطرمبه</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>تم الفك والتنظيف والتركيب</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">احمد عبدالعزيز </t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ميكانيكي</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_84e826d3_20260420_193315.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>دنابر محطه غزل1</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>كرد23</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -7422,176 +7409,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الصور</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>.55kwموتور</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ناقص زيت</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>تغير زيتpg1000
-تغير بليه 6204
-تغير بليه 6202
-تغير بليه 6201
-تغير اولسيه جروبوكس 80*40*10</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>شريف ,علي</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>روتاري فلتر</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>شحم</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>تم تشحيم الكراسي الفلتر شحم EB2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>شريف و عبد الحميد</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>بري فلتر</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>شحم</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>تم تشحيم الكراسي البري فلتر شحم EB2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>شريف وعبد الحميد</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8553,7 +8370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8775,6 +8592,52 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>شحم=Ep2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الصور</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8823,6 +8686,208 @@
           <t>الصور</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>الفواصل</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>تم تفريغ وغسل وملئ حوض</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الفواصل</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>تم تغير فواصل بلوك الاول</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنظيف شبك الدنابر </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>محروس،محمود،انس</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>الحوض</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم تفريغ الحوض وتنظيفه وملئه</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>الدنابر</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>تم تنظيف الشبك وغسله وتركيبه</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>علاء،الصادق</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8835,7 +8900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8869,208 +8934,6 @@
           <t>الصور</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>الطن</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>الفواصل</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>تم تفريغ وغسل وملئ حوض</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الفواصل</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>تم تغير فواصل بلوك الاول</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>علي,يوسف,محمود,احمد عبدالعزيز</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم تنظيف شبك الدنابر </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>محروس،محمود،انس</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>الحوض</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>تم تفريغ الحوض وتنظيفه وملئه</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">احمد عبدالعزيز </t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>الدنابر</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صيانه </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>تم تنظيف الشبك وغسله وتركيبه</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>علاء،الصادق</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -40,9 +40,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -73,9 +75,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3304,13 +3307,16 @@
       <c r="D23" t="n">
         <v>30</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" s="1" t="n">
-        <v>46136</v>
+      <c r="E23" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>فحص وتشحيم كتاين</t>
+          <t>فحص وتشحيم كتاين
+2026-04-29 | تم بواسطة: س</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -5092,7 +5098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5780,6 +5786,51 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_25421959_20260423_181555.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLU-1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'صيانه شهريه' بواسطة س</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -3276,13 +3276,16 @@
       <c r="D22" t="n">
         <v>30</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" s="1" t="n">
-        <v>46136</v>
+      <c r="E22" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>فحص وتشحيم كتاين</t>
+          <t>فحص وتشحيم كتاين
+2026-04-29 | تم بواسطة: س</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3310,7 +3313,7 @@
       <c r="E23" s="1" t="n">
         <v>46141</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -5098,7 +5101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5831,6 +5834,51 @@
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLU-2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'صيانه شهريه' بواسطة س</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -3113,15 +3113,16 @@
         <v>912.5</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>47037</v>
+        <v>46141</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>47053</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>زيتCLPPG680
-2026-04-13 | تم بواسطة: تيم الكرد</t>
+2026-04-13 | تم بواسطة: تيم الكرد
+2026-04-29 | تم بواسطة: س</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3279,7 +3280,7 @@
       <c r="E22" s="1" t="n">
         <v>46141</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -5101,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5879,6 +5880,51 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLX-2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تغير زيت جير بوكس درفيل العوادم</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير زيت جير بوكس درفيل العوادم' بواسطة س</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2194,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3829,6 +3832,91 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_f5bcc3f2_20260430_060915.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>مروحه راديال التنظيف</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>مروحه راديال كرد1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>مروحه راديال كرد2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>مروحه راديال تمشيط1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>مروحه راديال تمشيط2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22208,7 +22296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22881,13 +22969,16 @@
       <c r="D20" t="n">
         <v>30</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="F20" s="1" t="n">
-        <v>46136</v>
+        <v>46171</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>فحص وتشحيم كتاين</t>
+          <t>فحص وتشحيم كتاين
+2026-04-29 | تم بواسطة: تيم الكرد  | صورة: https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_c73050f5_20260430_174752.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -22912,13 +23003,16 @@
       <c r="D21" t="n">
         <v>30</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="F21" s="1" t="n">
-        <v>46136</v>
+        <v>46171</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>فحص وتشحيم كتاين</t>
+          <t>فحص وتشحيم كتاين
+2026-04-29 | تم بواسطة: تيم الكرد  | صورة: https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_988e39cd_20260430_174706.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -23917,6 +24011,288 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_15595bcd_20260430_062824.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21900 ساعة</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>تغير زيت جير بوكس حصيره اماميه</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>47052</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-04-28 | تم بواسطة: حسام،مصطفي | صورة: https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_28a239f2_20260430_175303.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_ed5cc2f9_20260430_175012.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21900 ساعة</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغير زيت جير بوكس حصيره مسننه تفتيح العوادم </t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>47052</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-28 | تم بواسطة: حسام،مصطفي | صورة: https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_65177400_20260430_175350.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_2d81cb17_20260430_175138.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BO-P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>30</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-29 | تم بواسطة: تيم الكرد</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>مروحه راديال التنظيف</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>صيانه شهريه (تشحيم+نظافه)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>30</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>شحمEP2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_34eebc92_20260430_180304.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>مروحه راديال كرد1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>صيانه شهريه (تشحيم+نظافه)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>30</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>شحمEP2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_f6b9171b_20260430_180339.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>مروحه راديال كرد2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>صيانه شهريه (تشحيم+نظافه)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>30</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>شحمEP2</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_14098a14_20260430_180415.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>مروحه راديال تمشيط1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>صيانه شهريه (تشحيم+نظافه)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>30</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>شحمEP2</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_01f27b66_20260430_180446.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>مروحه راديال تمشيط2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>صيانه شهريه (تشحيم+نظافه)</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>شحمEP2</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_0997f6e4_20260430_180530.jpg</t>
         </is>
       </c>
     </row>
@@ -23931,7 +24307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24752,6 +25128,264 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MIX-1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'صيانه شهريه' بواسطة تيم الكرد </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تيم الكرد </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_988e39cd_20260430_174706.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MIX-2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'صيانه شهريه' بواسطة تيم الكرد </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تيم الكرد </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_c73050f5_20260430_174752.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تغير زيت جير بوكس حصيره اماميه</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير زيت جير بوكس حصيره اماميه' بواسطة حسام،مصطفي</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>حسام،مصطفي</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_28a239f2_20260430_175303.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: تغير زيت جير بوكس حصيره مسننه تفتيح العوادم </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير زيت جير بوكس حصيره مسننه تفتيح العوادم ' بواسطة حسام،مصطفي</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>حسام،مصطفي</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_65177400_20260430_175350.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BO-P</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BO-P</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: صيانه شهريه</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'صيانه شهريه' بواسطة تيم الكرد </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تيم الكرد </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1586,106 @@
       <c r="N30" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_execution/maintenance_execution_55169538_20260430_062921.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>سيلو1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>قطع جنزير درافيل التغذيه</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم الفك والإصلاح وتركيب قفل جديد </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_5f473c4f_20260502_114034.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>مكبس السايلوهات</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>تم اعاده تركيب سولونويد ڤالڤ القديم بعد تنظيفه</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تيم المحطات </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_6ef2ab36_20260502_114829.jpg</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2003,6 +2100,101 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_85ea4b35_20260420_172837.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>سحب10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>سحب10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>تلف بليه6202</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>تم استبدال 2بليه6202</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>سحب10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>تلف سير1083</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>تم تركيب سير1083</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2197,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3917,6 +4109,53 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>دنابر محطه غزل1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم الفك والتنظيف والتركيب </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">احمد عبدالعزيز </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_6013632b_20260502_114257.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3929,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K511"/>
+  <dimension ref="A1:K513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21157,6 +21396,96 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr"/>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>كرد11</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>تلف سير 1200 فلات</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>تم استبدال سير 1200</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>رضا</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>3</v>
+      </c>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_74459f59_20260502_064233.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>كرد22</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>تلف بليه مضرب تفتيح dfk جنب شمال</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>تم للاستبدال وتركيب بليهUC207</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ف.محمود ايهاب </t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>3</v>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_5697bb83_20260502_113657.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21168,7 +21497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21200,6 +21529,290 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>الصور</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>كمبروسر 3كبير</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>زياره توكيل(صيانه شهريه)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم عمل نظافات. والفحص </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>م.رأفت،م.عبدالله،ف.عصام</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>آخر</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_a89ed90f_20260501_065629.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>كمبروسر 4كبير</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>زياره توكيل(صيانه شهريه)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم عمل نظافات. والفحص </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>م.رأفت،م.عبدالله،ف.عصام</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>آخر</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_eda36564_20260501_065653.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>كمبروسر 1صغير</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>زياره توكيل(صيانه شهريه)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم عمل نظافات. والفحص </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>م.رأفت،م.عبدالله،ف.عصام</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>آخر</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_3ef9004f_20260501_065940.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>كمبروسر 2صغير</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>زياره توكيل(صيانه شهريه)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم عمل نظافات. والفحص </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>م.رأفت،م.عبدالله،ف.عصام</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>آخر</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_b28d0aa8_20260501_070005.jpg</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21967,6 +22580,552 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_882dc9a7_20260422_210719.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>تمشيط18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>تمشيط18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم معايره المناجل والامشاط،وتشحيم </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>تمشيط 20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>تمشيط 4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>تمشيط 5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>تمشيط 20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>تم الصيانه والتشحيم</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>تلف سير1209</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>تم تركيب سير1209</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>تم تغير طاره الموتور الرئيسي</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>تمشيط 4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>تم تغير طاره الموتور الرئيسي</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>تمشيط 5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>تم تغير وصله هواء</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>تلف سير390</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>تم تركيب سير390</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>تلف سير1014</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>تم تركيب سير1014</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>تمشيط2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>تمشيط2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>تم تغير حامل بنز قطع ووصل</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابراهيم </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>تمشيط3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية:    اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية '   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق' بواسطة تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22296,7 +23455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24281,7 +25440,7 @@
         <v>30</v>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="G58" t="inlineStr">
@@ -24295,6 +25454,102 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/maintenance_task/maintenance_task_0997f6e4_20260430_180530.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>30</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>شحم Ep2
+2026-05-02 | تم بواسطة: تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>تمشيط3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>شحم Ep2</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>تمشيط2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>شحم Ep2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -20398,26 +20398,10 @@
           <t>22/1/2026</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>كرد24</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>قطع سير</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr">
-        <is>
-          <t>تم تغيير سير 700</t>
-        </is>
-      </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>رضا</t>
-        </is>
-      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr"/>
@@ -20431,26 +20415,10 @@
           <t>22/1/2026</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>كرد24</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>قطع سير</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr">
-        <is>
-          <t>تم تغيير سير 700</t>
-        </is>
-      </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>رضا</t>
-        </is>
-      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr"/>
       <c r="I484" t="inlineStr"/>
@@ -20464,26 +20432,10 @@
           <t>22/1/2026</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>كرد24</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>قطع سير</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>تم تغيير سير 700</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>رضا</t>
-        </is>
-      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
@@ -20497,26 +20449,10 @@
           <t>22/1/2026</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>كرد24</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>قطع سير</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>تم تغيير سير 700</t>
-        </is>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>رضا</t>
-        </is>
-      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
@@ -21429,8 +21365,10 @@
           <t>ميكانيكي</t>
         </is>
       </c>
-      <c r="I512" t="n">
-        <v>3</v>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
@@ -21472,8 +21410,10 @@
           <t>ميكانيكي</t>
         </is>
       </c>
-      <c r="I513" t="n">
-        <v>3</v>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
@@ -21998,7 +21938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23126,6 +23066,326 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>تمشيط6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>تمشيط1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ظبط مسافات واندكس</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>تمشيط3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ظبط مسافات واندكس</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>تمشيط2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>تغير 3 تروس تغذيه +4صاموله منجله</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>تمشيط13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>تغير بستم الباب</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>تمشيط 4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ضبط المسافات</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>تمشيط2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ضبط المسافات</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ابراهيم</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>تمشيط6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانة وقائية: (   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق)صيانه شهريه </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية '(   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق)صيانه شهريه ' بواسطة تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23371,7 +23631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23415,6 +23675,11 @@
           <t>قوه الشد</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23443,6 +23708,887 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>فلتر هواء كبير</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4E0304</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>فلتر زيت (كبيروصغير)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6.4693</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>شحم كيزر</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>زيت كيزر</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S_46*900132.00020</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>فلتر هواءصغير</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4E0302</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>فاصل زيت صغير</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>63623</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>فاصل زيت كبير</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6.4273</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>الضواغط</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير فرشه نازع امامي يوجد شمال ماكينه   </t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1,25 x 20 x 1014</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_5b9598f3_20260503_060547.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>سير نقل حركه من موتور دوفر يمين ماكينه</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1120   -   8M  -   20</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_09908b50_20260503_060919.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>سير حركه دوفر نفسه يمين مكنه</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1520   -   8M  -   20</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_c4fa446e_20260503_061102.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير مضرب تفتيح دفك </t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2,5 x 15 x   974</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_a46aec2c_20260503_061147.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>سير سلندر يمين مكنه</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2,0 x 50 x  3530</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_b8f35845_20260503_061234.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>سير  فيد رول يمين مكنه من خلف</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1800   -   8M  -   20</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_9ed5fde9_20260503_061340.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير نقل حركه من سلندر لليكر ان </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2,5 x 18 x  1200</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_3927d6e6_20260503_061436.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير عصارات خروج شريط امامي </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>700-D5M-15</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_a268668e_20260503_061545.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>سير  نقل حركه من دوفر لمجموعه نازع شريط اماميه</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1,8 x 12 x 753</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_61894784_20260503_061644.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>سير تحريك عصارتين خروج شريط يوجد داخل شاسيه امامي</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1,8 x  8 x  1800</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>سير تحرك رولين نازع بمنطقه دوفر</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1200-D8M-20</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_2e8b6dbe_20260503_061942.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>سير موتور عوادم خلفي  شمال مكنه</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18   -AT5   - 375</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير 3 ليكر ان </t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2,5 x 15 x  1350</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_157474f8_20260503_062229.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>سير فرشه  تنظيف فلاتس سريعه خلفيه</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1,3/1,25 x 15 x  550</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_cb13f86d_20260503_062325.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>سير فلتس مسنن</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>T10/3040</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>سير سحب شريط من ع سكويز رول</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 90*1280</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>سير فلات رصاص كويلر</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2,0 x 15 x  1465</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_e230a04b_20260503_062721.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير كويلر مسنن </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1270-D5M-15</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_6b5cc647_20260503_062904.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سير قاعده اسطوانه كويلر </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LW2310 CONTI-V FO PIONEER</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_86cdb89f_20260503_062951.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>سير نقل حركه من موتور للمضاربclx</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LW2900</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_1f30127d_20260503_064037.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>التفتيح</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>سير نقل حركه بين مضربين</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LW2700</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/spare_part/spare_part_e2ec95ca_20260503_064135.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>التفتيح</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23455,7 +24601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25550,6 +26696,39 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>تمشيط6</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(   اتشحيم سلندرات التغزيه والقطع والوصل وعمود الدعم والفرش والدرافت من فوق)صيانه شهريه </t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>30</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-03 | تم بواسطة: تيم التمشيط</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25562,7 +26741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26641,6 +27820,393 @@
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLU-1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_91f16b4a_20260503_113648.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLU-2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_b8668072_20260503_113713.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLX-1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_99edb16d_20260503_113802.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLX-2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_7778a667_20260503_113836.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MIX-1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_e165a6bd_20260503_113932.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MIX-2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_a87d094f_20260503_113955.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TS-T5-1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_a9271cbb_20260503_114045.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TS-T5-2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_d4ad9df3_20260503_114108.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BO-R</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>اداره مخاطر</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم تركيب حاجز حمايه </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>محمود الحداد ،م.شحته</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_ef1b28db_20260503_114201.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23631,7 +23631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,6 +23680,11 @@
           <t>القسم</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>حد_الإنذار</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23709,20 +23714,23 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>فلتر هواء كبير</t>
+          <t>فاصل زيت كبير</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4E0304</t>
+          <t>6.4273</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
@@ -23738,6 +23746,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23767,6 +23778,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23796,6 +23810,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23825,6 +23842,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23854,6 +23874,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23883,6 +23906,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23912,6 +23938,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23945,6 +23974,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23978,6 +24010,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24011,6 +24046,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24044,6 +24082,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24077,6 +24118,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24110,6 +24154,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24143,6 +24190,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24176,6 +24226,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24208,6 +24261,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -24238,6 +24294,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24270,6 +24329,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24300,6 +24362,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24333,6 +24398,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24365,6 +24433,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -24395,6 +24466,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24424,6 +24498,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24457,6 +24534,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24490,6 +24570,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24523,6 +24606,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24556,6 +24642,9 @@
           <t>التفتيح</t>
         </is>
       </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24588,6 +24677,9 @@
         <is>
           <t>التفتيح</t>
         </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23735,7 +23735,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23735,7 +23735,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23631,7 +23631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,11 +23680,6 @@
           <t>القسم</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>حد_الإنذار</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23714,23 +23709,20 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>فاصل زيت كبير</t>
+          <t>فلتر هواء كبير</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.4273</t>
+          <t>4E0304</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
@@ -23746,9 +23738,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23778,9 +23767,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23810,9 +23796,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23842,9 +23825,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23874,9 +23854,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23906,9 +23883,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23938,9 +23912,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23974,9 +23945,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24010,9 +23978,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24046,9 +24011,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24082,9 +24044,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24118,9 +24077,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24154,9 +24110,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24190,9 +24143,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24226,9 +24176,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24261,9 +24208,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -24294,9 +24238,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24329,9 +24270,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24362,9 +24300,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24398,9 +24333,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24433,9 +24365,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -24466,9 +24395,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24498,9 +24424,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24534,9 +24457,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24570,9 +24490,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24606,9 +24523,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24642,9 +24556,6 @@
           <t>التفتيح</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24677,9 +24588,6 @@
         <is>
           <t>التفتيح</t>
         </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23631,7 +23631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,6 +23680,11 @@
           <t>القسم</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>حد_الإنذار</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23709,6 +23714,9 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23738,6 +23746,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23767,6 +23778,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23796,6 +23810,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23825,6 +23842,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23854,6 +23874,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23883,6 +23906,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23901,7 +23927,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -23912,6 +23938,9 @@
           <t>الضواغط</t>
         </is>
       </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23945,6 +23974,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23978,6 +24010,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24011,6 +24046,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24044,6 +24082,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24077,6 +24118,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24110,6 +24154,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24143,6 +24190,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24176,6 +24226,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24208,6 +24261,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -24238,6 +24294,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24270,6 +24329,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24300,6 +24362,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24333,6 +24398,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24365,6 +24433,9 @@
         <is>
           <t>الكرد</t>
         </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -24395,6 +24466,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24424,6 +24498,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24457,6 +24534,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24490,6 +24570,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24523,6 +24606,9 @@
           <t>الكرد</t>
         </is>
       </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24556,6 +24642,9 @@
           <t>التفتيح</t>
         </is>
       </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24588,6 +24677,9 @@
         <is>
           <t>التفتيح</t>
         </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23939,7 +23939,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -23631,7 +23631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,11 +23680,6 @@
           <t>القسم</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>حد_الإنذار</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23714,9 +23709,6 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23746,9 +23738,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23778,9 +23767,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23810,9 +23796,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23842,9 +23825,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23874,9 +23854,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23906,9 +23883,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23927,7 +23901,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -23938,9 +23912,6 @@
           <t>الضواغط</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23974,9 +23945,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24010,9 +23978,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24046,9 +24011,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24082,9 +24044,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24118,9 +24077,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24154,9 +24110,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24190,9 +24143,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24226,9 +24176,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24261,9 +24208,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -24294,9 +24238,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24329,9 +24270,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24362,9 +24300,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24398,9 +24333,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24433,9 +24365,6 @@
         <is>
           <t>الكرد</t>
         </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -24466,9 +24395,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24498,9 +24424,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24534,9 +24457,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24570,9 +24490,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24606,9 +24523,6 @@
           <t>الكرد</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24642,9 +24556,6 @@
           <t>التفتيح</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24677,9 +24588,6 @@
         <is>
           <t>التفتيح</t>
         </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,36 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -497,6 +527,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -527,6 +563,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -537,6 +579,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,6 +615,50 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,32 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,32 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,44 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>يس</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>سس</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,44 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>بري فلتر</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
